--- a/reports/swing_performance.xlsx
+++ b/reports/swing_performance.xlsx
@@ -2746,7 +2746,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-04T16:32:09</t>
+          <t>2026-09-07T17:50:57</t>
         </is>
       </c>
     </row>

--- a/reports/swing_performance.xlsx
+++ b/reports/swing_performance.xlsx
@@ -2746,7 +2746,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-07T17:50:57</t>
+          <t>2026-09-08T16:47:49</t>
         </is>
       </c>
     </row>

--- a/reports/swing_performance.xlsx
+++ b/reports/swing_performance.xlsx
@@ -2746,7 +2746,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-08T16:47:49</t>
+          <t>2026-09-09T16:52:01</t>
         </is>
       </c>
     </row>

--- a/reports/swing_performance.xlsx
+++ b/reports/swing_performance.xlsx
@@ -2746,7 +2746,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09T16:52:01</t>
+          <t>2026-09-10T16:35:57</t>
         </is>
       </c>
     </row>

--- a/reports/swing_performance.xlsx
+++ b/reports/swing_performance.xlsx
@@ -2746,7 +2746,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-10T16:35:57</t>
+          <t>2026-09-11T16:41:18</t>
         </is>
       </c>
     </row>

--- a/reports/swing_performance.xlsx
+++ b/reports/swing_performance.xlsx
@@ -2746,7 +2746,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-11T16:41:18</t>
+          <t>2026-09-14T18:10:59</t>
         </is>
       </c>
     </row>

--- a/reports/swing_performance.xlsx
+++ b/reports/swing_performance.xlsx
@@ -2746,7 +2746,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-14T18:10:59</t>
+          <t>2026-09-15T17:13:00</t>
         </is>
       </c>
     </row>

--- a/reports/swing_performance.xlsx
+++ b/reports/swing_performance.xlsx
@@ -2746,7 +2746,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15T17:13:00</t>
+          <t>2026-09-16T17:12:14</t>
         </is>
       </c>
     </row>

--- a/reports/swing_performance.xlsx
+++ b/reports/swing_performance.xlsx
@@ -2746,7 +2746,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-16T17:12:14</t>
+          <t>2026-09-17T17:15:18</t>
         </is>
       </c>
     </row>

--- a/reports/swing_performance.xlsx
+++ b/reports/swing_performance.xlsx
@@ -2746,7 +2746,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-17T17:15:18</t>
+          <t>2026-09-18T16:37:31</t>
         </is>
       </c>
     </row>

--- a/reports/swing_performance.xlsx
+++ b/reports/swing_performance.xlsx
@@ -2746,7 +2746,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-18T16:37:31</t>
+          <t>2026-09-21T18:20:15</t>
         </is>
       </c>
     </row>

--- a/reports/swing_performance.xlsx
+++ b/reports/swing_performance.xlsx
@@ -2746,7 +2746,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-21T18:20:15</t>
+          <t>2026-09-22T17:08:15</t>
         </is>
       </c>
     </row>

--- a/reports/swing_performance.xlsx
+++ b/reports/swing_performance.xlsx
@@ -2746,7 +2746,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-22T17:08:15</t>
+          <t>2026-09-23T17:22:25</t>
         </is>
       </c>
     </row>

--- a/reports/swing_performance.xlsx
+++ b/reports/swing_performance.xlsx
@@ -2746,7 +2746,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-23T17:22:25</t>
+          <t>2026-09-24T17:25:12</t>
         </is>
       </c>
     </row>

--- a/reports/swing_performance.xlsx
+++ b/reports/swing_performance.xlsx
@@ -2746,7 +2746,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-24T17:25:12</t>
+          <t>2026-09-25T17:25:04</t>
         </is>
       </c>
     </row>

--- a/reports/swing_performance.xlsx
+++ b/reports/swing_performance.xlsx
@@ -2746,7 +2746,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-25T17:25:04</t>
+          <t>2026-09-28T19:48:55</t>
         </is>
       </c>
     </row>

--- a/reports/swing_performance.xlsx
+++ b/reports/swing_performance.xlsx
@@ -2746,7 +2746,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-28T19:48:55</t>
+          <t>2026-09-29T18:13:56</t>
         </is>
       </c>
     </row>

--- a/reports/swing_performance.xlsx
+++ b/reports/swing_performance.xlsx
@@ -2746,7 +2746,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29T18:13:56</t>
+          <t>2026-09-30T18:04:59</t>
         </is>
       </c>
     </row>

--- a/reports/swing_performance.xlsx
+++ b/reports/swing_performance.xlsx
@@ -2746,7 +2746,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-30T18:04:59</t>
+          <t>2026-10-01T18:34:08</t>
         </is>
       </c>
     </row>

--- a/reports/swing_performance.xlsx
+++ b/reports/swing_performance.xlsx
@@ -2746,7 +2746,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01T18:34:08</t>
+          <t>2026-10-02T17:58:42</t>
         </is>
       </c>
     </row>

--- a/reports/swing_performance.xlsx
+++ b/reports/swing_performance.xlsx
@@ -2746,7 +2746,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02T17:58:42</t>
+          <t>2026-10-05T20:45:22</t>
         </is>
       </c>
     </row>

--- a/reports/swing_performance.xlsx
+++ b/reports/swing_performance.xlsx
@@ -2746,7 +2746,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-05T20:45:22</t>
+          <t>2026-10-06T18:35:04</t>
         </is>
       </c>
     </row>

--- a/reports/swing_performance.xlsx
+++ b/reports/swing_performance.xlsx
@@ -2746,7 +2746,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06T18:35:04</t>
+          <t>2026-10-07T19:03:45</t>
         </is>
       </c>
     </row>

--- a/reports/swing_performance.xlsx
+++ b/reports/swing_performance.xlsx
@@ -2746,7 +2746,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-07T19:03:45</t>
+          <t>2026-10-08T18:59:55</t>
         </is>
       </c>
     </row>

--- a/reports/swing_performance.xlsx
+++ b/reports/swing_performance.xlsx
@@ -2746,7 +2746,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-08T18:59:55</t>
+          <t>2026-10-09T18:31:11</t>
         </is>
       </c>
     </row>

--- a/reports/swing_performance.xlsx
+++ b/reports/swing_performance.xlsx
@@ -2746,7 +2746,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-09T18:31:11</t>
+          <t>2026-10-12T21:24:53</t>
         </is>
       </c>
     </row>

--- a/reports/swing_performance.xlsx
+++ b/reports/swing_performance.xlsx
@@ -2746,7 +2746,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-12T21:24:53</t>
+          <t>2026-10-13T19:30:02</t>
         </is>
       </c>
     </row>

--- a/reports/swing_performance.xlsx
+++ b/reports/swing_performance.xlsx
@@ -2746,7 +2746,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-13T19:30:02</t>
+          <t>2026-10-14T17:28:50</t>
         </is>
       </c>
     </row>

--- a/reports/swing_performance.xlsx
+++ b/reports/swing_performance.xlsx
@@ -2746,7 +2746,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14T17:28:50</t>
+          <t>2026-10-15T17:15:44</t>
         </is>
       </c>
     </row>

--- a/reports/swing_performance.xlsx
+++ b/reports/swing_performance.xlsx
@@ -2746,7 +2746,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-15T17:15:44</t>
+          <t>2026-10-16T16:54:17</t>
         </is>
       </c>
     </row>

--- a/reports/swing_performance.xlsx
+++ b/reports/swing_performance.xlsx
@@ -2746,7 +2746,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-16T16:54:17</t>
+          <t>2026-10-19T18:49:38</t>
         </is>
       </c>
     </row>

--- a/reports/swing_performance.xlsx
+++ b/reports/swing_performance.xlsx
@@ -2746,7 +2746,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-19T18:49:38</t>
+          <t>2026-10-20T17:27:36</t>
         </is>
       </c>
     </row>

--- a/reports/swing_performance.xlsx
+++ b/reports/swing_performance.xlsx
@@ -2746,7 +2746,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-20T17:27:36</t>
+          <t>2026-10-21T17:29:00</t>
         </is>
       </c>
     </row>

--- a/reports/swing_performance.xlsx
+++ b/reports/swing_performance.xlsx
@@ -2746,7 +2746,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-21T17:29:00</t>
+          <t>2026-10-22T17:25:13</t>
         </is>
       </c>
     </row>

--- a/reports/swing_performance.xlsx
+++ b/reports/swing_performance.xlsx
@@ -2746,7 +2746,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-22T17:25:13</t>
+          <t>2026-10-23T17:22:14</t>
         </is>
       </c>
     </row>

--- a/reports/swing_performance.xlsx
+++ b/reports/swing_performance.xlsx
@@ -2746,7 +2746,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-23T17:22:14</t>
+          <t>2026-10-26T18:48:09</t>
         </is>
       </c>
     </row>

--- a/reports/swing_performance.xlsx
+++ b/reports/swing_performance.xlsx
@@ -2746,7 +2746,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-26T18:48:09</t>
+          <t>2026-10-27T18:12:57</t>
         </is>
       </c>
     </row>

--- a/reports/swing_performance.xlsx
+++ b/reports/swing_performance.xlsx
@@ -2746,7 +2746,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-27T18:12:57</t>
+          <t>2026-10-28T18:27:00</t>
         </is>
       </c>
     </row>

--- a/reports/swing_performance.xlsx
+++ b/reports/swing_performance.xlsx
@@ -2746,7 +2746,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-28T18:27:00</t>
+          <t>2026-10-29T18:39:21</t>
         </is>
       </c>
     </row>

--- a/reports/swing_performance.xlsx
+++ b/reports/swing_performance.xlsx
@@ -2746,7 +2746,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-29T18:39:21</t>
+          <t>2026-10-30T18:11:02</t>
         </is>
       </c>
     </row>
